--- a/checklist_forms/046_tape_in_hair_extension_placement_checklist--checklist_forms.xlsx
+++ b/checklist_forms/046_tape_in_hair_extension_placement_checklist--checklist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'micro_loop'}</t>
+          <t>micro_loop</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Micro Loop'}</t>
+          <t>Micro Loop</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tape_in'}</t>
+          <t>tape_in</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tape in'}</t>
+          <t>Tape in</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'hair_bond'}</t>
+          <t>hair_bond</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Hair Bond'}</t>
+          <t>Hair Bond</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Long'}</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'hand-tied'}</t>
+          <t>hand-tied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Hand-tied'}</t>
+          <t>Hand-tied</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'root'}</t>
+          <t>root</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Root'}</t>
+          <t>Root</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'micro'}</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Micro'}</t>
+          <t>Micro</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'stick-tie'}</t>
+          <t>stick-tie</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Stick-Tie'}</t>
+          <t>Stick-Tie</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'back'}</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Back'}</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sides'}</t>
+          <t>sides</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sides'}</t>
+          <t>Sides</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'top'}</t>
+          <t>top</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Top'}</t>
+          <t>Top</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'front'}</t>
+          <t>front</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Front'}</t>
+          <t>Front</t>
         </is>
       </c>
     </row>
